--- a/public/templates/forms/A-087-TrainingCompletionRecords-FORM.xlsx
+++ b/public/templates/forms/A-087-TrainingCompletionRecords-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -206,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -265,6 +270,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -595,7 +603,7 @@
       <c r="E5" s="21" t="n"/>
       <c r="F5" s="20" t="n"/>
     </row>
-    <row r="6" ht="43.5" customHeight="1">
+    <row r="6" ht="66.4" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -611,7 +619,7 @@
       <c r="E6" s="21" t="n"/>
       <c r="F6" s="20" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="113.9" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage / Scope</t>
@@ -634,14 +642,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>« One row per person per course completed. Record general awareness and role-based training here, using the Track column to tell them apart. Keep the current and prior year, and report completion against the leadership-set target in the Findings block. »</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Staff Member (Name &amp; Role)</t>
@@ -815,7 +823,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="34.7" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>[Completion against target for the period: [X]% of staff current on required training versus the [Y]% target set by leadership. List anyone overdue and the plan to close the gap. Report this summary to leadership on the review cycle.]</t>
@@ -947,7 +955,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="34.7" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Version</t>
@@ -995,10 +1003,10 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="66.4" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Drafter's note (internal, delete before publishing): Log/Record form, build-order #69 (A-087). One log covers general awareness and role-based training, split by the Track column; Staff Member combines name and role per the register precedent. CJIS security awareness completion is tracked in its own record and cross-referenced here, not duplicated. Completion-against-target reporting to leadership lives in the Findings block. Classification Confidential / CJIS per the Tracker.</t>
+          <t>Drafter's note (internal, delete before publishing): Log/Record form, build-order #69. One log covers general awareness and role-based training, split by the Track column; Staff Member combines name and role per the register precedent. CJIS security awareness completion is tracked in its own record and cross-referenced here, not duplicated. Completion-against-target reporting to leadership lives in the Findings block. Classification Confidential / CJIS per the Tracker.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1043,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1061,14 +1069,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: record each completed course, one row per person per course. Use the Track column to separate general awareness from role-based training, and report completion against the leadership-set target in the Findings block. Replace every [BRACKETED] field and delete every « » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -1104,7 +1112,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="50.5" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Staff Member (Name &amp; Role)</t>
@@ -1148,7 +1156,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Track (General / Role-based)</t>
@@ -1186,10 +1194,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D10" s="24">
+        <v>46082</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1230,10 +1236,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
+      <c r="D12" s="24">
+        <v>46447</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1322,6 +1326,6 @@
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>